--- a/price_bank/test/fixtures/99999-SMP-ME-RE-476_R03_MTO_and_Cost_Estimation_Report.xlsx
+++ b/price_bank/test/fixtures/99999-SMP-ME-RE-476_R03_MTO_and_Cost_Estimation_Report.xlsx
@@ -16,9 +16,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TANKS-A (1)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HEATERS-A" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIR COMP." sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOTAL" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INS-VESSEL-A" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INS-TANK-A (1)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIR DRYER" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C.I.P.-A (1)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRANES (1)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FLARE-A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK-A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BURN PIT IGNITION-A" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FILTERS-A" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R.O." sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STRIPPER-B" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHILLING UNIT (DEAERATOR)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IWWTP-A (1)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC-TITLE" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOTAL" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INS-VESSEL-A" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INS-TANK-A (1)" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,6 +882,5249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:BH32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>58</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AIR DRYER PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH &amp; SOUTH TRAINS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-212</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Air Dryer Packages</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>553699747</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>553699747</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Type: Adsorber (heatless-pressure swig)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Drying Medium : Solid Desicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Inlet Flow Rate (m3/hr): 510</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Design Pressure: 13 Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 85 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tower Qty.: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>No. of Pre-Filter Req'd: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No. of After-Filter Req'd: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Material: C.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>553699747</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32"/>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AK31:AP32"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="U19:AB30"/>
+    <mergeCell ref="AW19:BH30"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="AQ31:AV32"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AC31:AJ32"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AQ19:AV30"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AC19:AJ30"/>
+    <mergeCell ref="U31:AB32"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="AK19:AP30"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A19:E30"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="R19:T30"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHEMICAL INJECTION PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-250</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Anti Scale Injection Package</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1617818032</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1617818032</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Max. Injection Rate (Lit/hr): 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Max. Discharge Pressure (Barg): 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pumps Qty.: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pumps Material: S.S. 316 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pumps Design Code &amp; Standard: API 675</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-PM-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tank Capacity (m3): 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tank Design Pressure (Barg): 3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tank Design Temperature (oC): -2 / 55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tank Material: S.S. 316 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Agitator Required: Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tank Design Code &amp; Standard: </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ASME VIII, DIV.1 &amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PK-251</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Demulsifier Injection Package</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2353403858</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2353403858</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Max. Injection Rate (Lit/hr): 85</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Max. Discharge Pressure (Barg): 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pumps Qty.: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pumps Material: S.S. 316 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pumps Design Code &amp; Standard: API 675</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-PM-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tank Capacity (m3): 2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tank Design Pressure (Barg): 3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tank Design Temperature (oC): -2 / 55</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tank Material: S.S. 316 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Agitator Required: Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tank Design Code &amp; Standard: </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ASME VIII, DIV.1 &amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="77">
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="A19:E32"/>
+    <mergeCell ref="F36:Q36"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="F45:Q45"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="F46:Q46"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="F39:Q39"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="AK19:AP32"/>
+    <mergeCell ref="F21:Q21"/>
+    <mergeCell ref="F41:Q41"/>
+    <mergeCell ref="AQ33:AV46"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AQ19:AV32"/>
+    <mergeCell ref="AC33:AJ46"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="AC19:AJ32"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="F40:Q40"/>
+    <mergeCell ref="AW19:BH32"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="F35:Q35"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AK33:AP46"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="F37:Q37"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="F44:Q44"/>
+    <mergeCell ref="F34:Q34"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="U33:AB46"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="F42:Q42"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="U19:AB32"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="AW33:BH46"/>
+    <mergeCell ref="F43:Q43"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="R33:T46"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="A33:E46"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="R19:T32"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="BD10:BE11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>59</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OVERHEAD TRAVELING CRANES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH &amp; SOUTH TRAINS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CN-114 / CN-124</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Main Pumps Shelter Cranes</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3422602226</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4168497024</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Type: Top Running, Elect. Motor Driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Capacity (Kg): 5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lift / Span / Travel (m): 5.8 / 9.15 / 85</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motor Charactristics: IP65- 400V,3Ph,50Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>&amp; EEX-e, IIB, T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: BSI 466</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-GN-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CN-151</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Utility Building Crane</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1114803250</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1114803250</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Type: Top Running, Elect. Motor Driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Capacity (Kg): 5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lift / Span / Travel (m): 5.8 / 8.15 / 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motor Charactristics: IP65- 400V,3Ph,50Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: BSI 466</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-GN-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CN-231</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>O.W.S. Pumps Shelter Crane</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>544668144</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>544668144</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Type: Top Running, Elect. Motor Driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Capacity (Kg): 3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lift / Span / Travel (m): 3.8 / 4.15 / 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Motor Charactristics: IP65- 400V,3Ph,50Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: BSI 466</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-GN-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CN-251 / CN-261</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Chemical Storage Shelter Cranes</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2358123753</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4211951555</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Type: Top Running, Elect. Motor Driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Capacity (Kg): 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lift / Span / Travel (m): 5.6 / 5.15 / 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motor Charactristics: IP65- 400V,3Ph,50Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>&amp; EEX-e, IIB, T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: BSI 466</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-GN-350</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="93">
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="F36:Q36"/>
+    <mergeCell ref="AW27:BH33"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="F45:Q45"/>
+    <mergeCell ref="AK41:AP48"/>
+    <mergeCell ref="A41:E48"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F47:Q47"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="R27:T33"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="F46:Q46"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="F39:Q39"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="F48:Q48"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AQ41:AV48"/>
+    <mergeCell ref="A19:E26"/>
+    <mergeCell ref="AK19:AP26"/>
+    <mergeCell ref="AK34:AP40"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="U19:AB26"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="F21:Q21"/>
+    <mergeCell ref="AC34:AJ40"/>
+    <mergeCell ref="F41:Q41"/>
+    <mergeCell ref="AC27:AJ33"/>
+    <mergeCell ref="AW41:BH48"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="AW34:BH40"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="AK27:AP33"/>
+    <mergeCell ref="AC41:AJ48"/>
+    <mergeCell ref="F40:Q40"/>
+    <mergeCell ref="AQ34:AV40"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="AQ27:AV33"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="F35:Q35"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="AC19:AJ26"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="F37:Q37"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="F44:Q44"/>
+    <mergeCell ref="F34:Q34"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="AW19:BH26"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="F42:Q42"/>
+    <mergeCell ref="R34:T40"/>
+    <mergeCell ref="R41:T48"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="U41:AB48"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="A34:E40"/>
+    <mergeCell ref="AQ19:AV26"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="F43:Q43"/>
+    <mergeCell ref="U34:AB40"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="R19:T26"/>
+    <mergeCell ref="U27:AB33"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="A27:E33"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="BD10:BE11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>51</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FLARE PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-171</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flare Package</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4371567647</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4371567647</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Total Capacity (Kg/hr): 19912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ignition System Type: Flame Front Gen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>(Compressed Air)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stack Size (D x H): 20 in x 12 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stack Support System: Self-Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: API RP 521,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>API-537, ASME STS-1,  IPS-G-ME-210,</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &amp; IPS-E-PR-460 </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>4371567647</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29"/>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="U28:AB29"/>
+    <mergeCell ref="AQ28:AV29"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AC19:AJ27"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="R19:T27"/>
+    <mergeCell ref="A19:E27"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AK19:AP27"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="AW19:BH27"/>
+    <mergeCell ref="U19:AB27"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AK28:AP29"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="AQ19:AV27"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AC28:AJ29"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>53</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STACKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ST-172</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cold Vent Stack</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>254080847</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>254080847</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Size (D x H): 20 in x 10000 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Type: Self Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Design Pressure: 3.5 Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 125 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Material (Shell): SA 516 Gr. 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design Code &amp; Standard: ASME STS-1 </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>/ API 537 / IPS-G-ME-210 / IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ASME VIII , DIV. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>254080847</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29"/>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="U28:AB29"/>
+    <mergeCell ref="AQ28:AV29"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AC19:AJ27"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="R19:T27"/>
+    <mergeCell ref="AK19:AP27"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="A19:E27"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="AW19:BH27"/>
+    <mergeCell ref="U19:AB27"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AK28:AP29"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="AQ19:AV27"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AC28:AJ29"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BURN PIT IGNITION PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+'FOB' (€)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price 'FOB' (€)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-231</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Burn Pit Ignition Package</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2353403858</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2353403858</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ignition System Type: Flame Front Gen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>(Compressed Air)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Burn Pit Diameter: 12.5 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Electrical Duty: 1.2 KW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Min. Elect. Equip. Protection: IP 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>2353403858</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26"/>
+  </sheetData>
+  <mergeCells count="52">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="U25:AB26"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="AQ19:AV24"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AC25:AJ26"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="AC19:AJ24"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AK25:AP26"/>
+    <mergeCell ref="AQ25:AV26"/>
+    <mergeCell ref="R19:T24"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A19:E24"/>
+    <mergeCell ref="AK19:AP24"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AW19:BH24"/>
+    <mergeCell ref="U19:AB24"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>49</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FILTERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-132</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nutshell Filter Package</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>279554</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>279554</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Type: Auotomatic Backwashable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Including: 3 x 50% Filter Vessels</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rated Flow Rate (m3/hr): 340</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Discharge Free Oil Content (ppmw): 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Design Pressure: 10.3 Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 95 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Material (Shell/Heads): SA 516 Gr. 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Material (Internal Wetted Parts): Duplex S.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Agitator Required: Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F-151</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sealing Water Filter</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1114803250</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1114803250</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Type: Auotomatic Self Cleaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Flow Rate: 3 x 1.1 m3/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Design Pressure: 17.7 Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 85 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Material (Shell/Heads): C.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>1114803250</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
+        <v>279554</v>
+      </c>
+    </row>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="73">
+    <mergeCell ref="AC39:AJ40"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AW19:BH30"/>
+    <mergeCell ref="U19:AB30"/>
+    <mergeCell ref="F36:Q36"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="AK31:AP38"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="F35:Q35"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="AQ31:AV38"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="AW31:BH38"/>
+    <mergeCell ref="U39:AB40"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="F37:Q37"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AC31:AJ38"/>
+    <mergeCell ref="AQ19:AV30"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AC19:AJ30"/>
+    <mergeCell ref="AK39:AP40"/>
+    <mergeCell ref="A31:E38"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="AK19:AP30"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="F34:Q34"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="R31:T38"/>
+    <mergeCell ref="AQ39:AV40"/>
+    <mergeCell ref="A19:E30"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="R19:T30"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="U31:AB38"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>62</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REVERSE OSMOSIS PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH &amp; SOUTH TRAINS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-152</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse Osmosis Packages </t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>997550194</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>997550194</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Capacity (m3/hr): 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Including: Back Filters, R.O. Unit, C.I.P.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Chemical Injection System &amp; U.V. Lamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>997550194</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24"/>
+  </sheetData>
+  <mergeCells count="50">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AQ19:AV22"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="AC23:AJ24"/>
+    <mergeCell ref="AK23:AP24"/>
+    <mergeCell ref="AC19:AJ22"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="R19:T22"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="AK19:AP22"/>
+    <mergeCell ref="A19:E22"/>
+    <mergeCell ref="U23:AB24"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="U19:AB22"/>
+    <mergeCell ref="AW19:BH22"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AQ23:AV24"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>43</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STRIPPING PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SOUTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-143</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stripping Package</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>8413976134</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8413976134</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Including Strpper Towers,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stripped Waste Water Pumps,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Related Piping, Instruments, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Strpper Towers Tag Nos.: T-143 A/B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Internals: Packing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lower Sec. Dim. (ID x L): 2000 x 2500 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Upper Sec. Dim. (ID x L): 800 x 5000 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Total Length: 9000 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Design Pressure: 5 (F.V.) Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 95 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mat. (Shell/Heads): SA 516 Gr. 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mat. (Remov. Internals): Duplex S.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design Code &amp; Standard: </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ASME VIII, DIV.1 &amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stripped Waste Water Pumps </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tag Nos.: P-148 A/B/C</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pumps Type: Centrifugal (OH2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pumps Rated Flow (m3/hr): 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pumps Differential Pressure (Barg): 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pumps Material Class(Acc. to API 610): D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pumps Design Code &amp; Standard: API 610</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-PM-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>8413976134</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43"/>
+  </sheetData>
+  <mergeCells count="69">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AC42:AJ43"/>
+    <mergeCell ref="F36:Q36"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="F41:Q41"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="F35:Q35"/>
+    <mergeCell ref="AW19:BH41"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="AK42:AP43"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="U42:AB43"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AQ19:AV41"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="F39:Q39"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="F37:Q37"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="AC19:AJ41"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="AQ42:AV43"/>
+    <mergeCell ref="F34:Q34"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="R19:T41"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="A19:E41"/>
+    <mergeCell ref="AK19:AP41"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="F40:Q40"/>
+    <mergeCell ref="U19:AB41"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DEAERATION PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+'FOB' (€)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price 'FOB' (€)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E-151</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Chilling Unit (Deaeration System)</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2070334480</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2070334480</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>The mentioned capacity shall be confirmed &amp; finalized by Deaerator Vendor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Type: Air-cooled H.E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Flow Rate (m3/hr): 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>2070334480</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23"/>
+  </sheetData>
+  <mergeCells count="48">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="A19:E21"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="AW19:BH21"/>
+    <mergeCell ref="U19:AB21"/>
+    <mergeCell ref="R19:T21"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A13:BH14"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="AC22:AJ23"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="U22:AB23"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AQ19:AV21"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="AQ22:AV23"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="AC19:AJ21"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="AK19:AP21"/>
+    <mergeCell ref="AK22:AP23"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VESSELS </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>V-171</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flare K.O. Drum</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>997550194</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>997550194</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Size (ID x TL-TL): 1500 x 4500 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Installation Position: Horizontal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Design Pressure: 3.5 (F.V.) Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 95 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Material (Shell/Heads): SA 516 Gr. 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>V-231</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Closed Drain Drum</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1518677236</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1518677236</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Size (ID x TL-TL): 2000 x 8000 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Installation Position: Horizontal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Design Pressure: 3.5 (F.V.) Barg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Design Temperature: -2 / 95 oC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Material (Shell/Heads): SA 516 Gr. 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Total Price (Rials)</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>2355493864</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Total Price (Euros)</t>
+        </is>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36"/>
+  </sheetData>
+  <mergeCells count="69">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="U27:AB34"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="AC35:AJ36"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AQ19:AV26"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="A27:E34"/>
+    <mergeCell ref="AK27:AP34"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="AC19:AJ26"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="AW27:BH34"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="U35:AB36"/>
+    <mergeCell ref="AQ35:AV36"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="R19:T26"/>
+    <mergeCell ref="AQ27:AV34"/>
+    <mergeCell ref="A19:E26"/>
+    <mergeCell ref="AK19:AP26"/>
+    <mergeCell ref="AC27:AJ34"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="F34:Q34"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="R27:T34"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="U19:AB26"/>
+    <mergeCell ref="AW19:BH26"/>
+    <mergeCell ref="AK35:AP36"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>45</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IGF PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NORTH TRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Qty.
+(Set)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Rials)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Unit Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Total Price
+(Euros)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PK-131</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>IGF Package</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1004172</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1004172</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Design Flow (m3/hr): 340</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Including IGF Vessel, </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pumps (Water Recycle, De-oiled </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Water Booster, Recovered Waste Oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp; Oily Sludge), </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Related Piping, Instruments, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vessel Design Pressure (Barg): 5 (F.V.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vessel Design Temperature (oC): 95</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vessel Mat. (Shell/Heads): SA 516 Gr.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Removable Internals Mat.: Duplex S.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vessel Design Codes &amp; Standards:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ASME VIII, DIV.1 &amp; IPS-G-ME-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Water Recycle Pumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Type: Centrifugal (OH2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Material Class(Acc. to API 610): D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: API 610</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-PM-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>De-oiled Water Booster Pumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Type: Centrifugal (OH2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Material Class(Acc. to API 610): D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: API 610</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>&amp; IPS-G-PM-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Recovered Waste Oil Pumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Type: P.D.-Rotary (Ext. Gear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Material Class(Acc. to API 610): D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Design Code &amp; Standard: API 676</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>&amp; IPS-M-PM-140</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+  </sheetData>
+  <mergeCells count="75">
+    <mergeCell ref="R16:T18"/>
+    <mergeCell ref="AQ19:AV51"/>
+    <mergeCell ref="AQ16:AV18"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="F51:Q51"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="F20:Q20"/>
+    <mergeCell ref="F24:Q24"/>
+    <mergeCell ref="F42:Q42"/>
+    <mergeCell ref="F36:Q36"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="F45:Q45"/>
+    <mergeCell ref="AC19:AJ51"/>
+    <mergeCell ref="F41:Q41"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="AK19:AP51"/>
+    <mergeCell ref="F50:Q50"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="R19:T51"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="F35:Q35"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="AC16:AJ18"/>
+    <mergeCell ref="F47:Q47"/>
+    <mergeCell ref="F16:Q18"/>
+    <mergeCell ref="F23:Q23"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="A19:E51"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="F46:Q46"/>
+    <mergeCell ref="F22:Q22"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="F27:Q27"/>
+    <mergeCell ref="AW19:BH51"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="AK16:AP18"/>
+    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="F43:Q43"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="F37:Q37"/>
+    <mergeCell ref="F39:Q39"/>
+    <mergeCell ref="F48:Q48"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="AW16:BH18"/>
+    <mergeCell ref="U16:AB18"/>
+    <mergeCell ref="A14:BH14"/>
+    <mergeCell ref="U19:AB51"/>
+    <mergeCell ref="F49:Q49"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="F44:Q44"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="F34:Q34"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A13:BH13"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="F25:Q25"/>
+    <mergeCell ref="F40:Q40"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="BD10:BE11"/>
+    <mergeCell ref="F21:Q21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Basic Design Study and FEED Package
+Preparation for Construct New SAMPLE
+(NORTH &amp; SOUTH) Desalting Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Consultant Co.</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project No.: 00-00-99999</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document Title : 
+MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Contract No.: 00-00-0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Consult. Proj. No.: 0000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Loc.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Disc.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Seq.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page No: </t>
+        </is>
+      </c>
+      <c r="BB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="n">
+        <v>86273</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>476</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PROCUREMENT 
+MTO &amp; COST ESTIMATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="AF10:AK10"/>
+    <mergeCell ref="AW7:BH9"/>
+    <mergeCell ref="AW1:BH4"/>
+    <mergeCell ref="AW10:BA11"/>
+    <mergeCell ref="A1:M4"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="N7:AV9"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="AR10:AV10"/>
+    <mergeCell ref="BF10:BG11"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="N1:AV6"/>
+    <mergeCell ref="AL10:AQ10"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A13:BH51"/>
+    <mergeCell ref="AW5:BH6"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A10:M11"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="A7:M9"/>
+    <mergeCell ref="AL11:AQ11"/>
+    <mergeCell ref="BB10:BC11"/>
+    <mergeCell ref="BD10:BE11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:BH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1952,7 +7207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2343,7 +7598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2806,445 +8061,6 @@
     <mergeCell ref="BB10:BC11"/>
     <mergeCell ref="AI21:AK22"/>
     <mergeCell ref="BD10:BE11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:BH36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Basic Design Study and FEED Package
-Preparation for Construct New SAMPLE
-(NORTH &amp; SOUTH) Desalting Unit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Consultant Co.</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Project No.: 00-00-99999</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Document Title : 
-MECH. BASIC DESIGN MTO &amp; COST ESTIMATION REPORT</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Contract No.: 00-00-0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Consult. Proj. No.: 0000</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Proj.</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Loc.</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Disc.</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Seq.</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Rev.</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page No: </t>
-        </is>
-      </c>
-      <c r="BB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>of</t>
-        </is>
-      </c>
-      <c r="BF10" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="N11" t="n">
-        <v>86273</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>KPL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="AL11" t="n">
-        <v>476</v>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VESSELS </t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NORTH TRAIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Qty.
-(Set)</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Unit Price
-(Rials)</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Total Price
-(Rials)</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Unit Price
-(Euros)</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Total Price
-(Euros)</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>V-171</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Flare K.O. Drum</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>997550194</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>997550194</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Size (ID x TL-TL): 1500 x 4500 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Installation Position: Horizontal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Design Pressure: 3.5 (F.V.) Barg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Design Temperature: -2 / 95 oC</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Material (Shell/Heads): SA 516 Gr. 70</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>&amp; IPS-G-ME-150</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>V-231</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Closed Drain Drum</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1518677236</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1518677236</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Size (ID x TL-TL): 2000 x 8000 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Installation Position: Horizontal</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Design Pressure: 3.5 (F.V.) Barg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Design Temperature: -2 / 95 oC</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Material (Shell/Heads): SA 516 Gr. 70</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Design Code &amp; Standard: ASME VIII, DIV.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>&amp; IPS-G-ME-150</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Total Price (Rials)</t>
-        </is>
-      </c>
-      <c r="AC35" t="n">
-        <v>2355493864</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Total Price (Euros)</t>
-        </is>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36"/>
-  </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="R16:T18"/>
-    <mergeCell ref="AQ16:AV18"/>
-    <mergeCell ref="T10:Y10"/>
-    <mergeCell ref="F20:Q20"/>
-    <mergeCell ref="AF10:AK10"/>
-    <mergeCell ref="F24:Q24"/>
-    <mergeCell ref="AW7:BH9"/>
-    <mergeCell ref="F33:Q33"/>
-    <mergeCell ref="AW1:BH4"/>
-    <mergeCell ref="U27:AB34"/>
-    <mergeCell ref="F32:Q32"/>
-    <mergeCell ref="F26:Q26"/>
-    <mergeCell ref="AC35:AJ36"/>
-    <mergeCell ref="AW10:BA11"/>
-    <mergeCell ref="A1:M4"/>
-    <mergeCell ref="T11:Y11"/>
-    <mergeCell ref="AC16:AJ18"/>
-    <mergeCell ref="F16:Q18"/>
-    <mergeCell ref="F23:Q23"/>
-    <mergeCell ref="N7:AV9"/>
-    <mergeCell ref="AQ19:AV26"/>
-    <mergeCell ref="AF11:AK11"/>
-    <mergeCell ref="F28:Q28"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="F31:Q31"/>
-    <mergeCell ref="F22:Q22"/>
-    <mergeCell ref="A27:E34"/>
-    <mergeCell ref="AK27:AP34"/>
-    <mergeCell ref="AR10:AV10"/>
-    <mergeCell ref="AC19:AJ26"/>
-    <mergeCell ref="F27:Q27"/>
-    <mergeCell ref="AW27:BH34"/>
-    <mergeCell ref="BF10:BG11"/>
-    <mergeCell ref="AK16:AP18"/>
-    <mergeCell ref="A16:E18"/>
-    <mergeCell ref="Z10:AE10"/>
-    <mergeCell ref="U35:AB36"/>
-    <mergeCell ref="AQ35:AV36"/>
-    <mergeCell ref="A5:M6"/>
-    <mergeCell ref="N1:AV6"/>
-    <mergeCell ref="AL10:AQ10"/>
-    <mergeCell ref="U16:AB18"/>
-    <mergeCell ref="AW16:BH18"/>
-    <mergeCell ref="A14:BH14"/>
-    <mergeCell ref="R19:T26"/>
-    <mergeCell ref="AQ27:AV34"/>
-    <mergeCell ref="A19:E26"/>
-    <mergeCell ref="AK19:AP26"/>
-    <mergeCell ref="AC27:AJ34"/>
-    <mergeCell ref="AW5:BH6"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="F29:Q29"/>
-    <mergeCell ref="A10:M11"/>
-    <mergeCell ref="F34:Q34"/>
-    <mergeCell ref="Z11:AE11"/>
-    <mergeCell ref="F19:Q19"/>
-    <mergeCell ref="AR11:AV11"/>
-    <mergeCell ref="A13:BH13"/>
-    <mergeCell ref="A7:M9"/>
-    <mergeCell ref="R27:T34"/>
-    <mergeCell ref="AL11:AQ11"/>
-    <mergeCell ref="F25:Q25"/>
-    <mergeCell ref="U19:AB26"/>
-    <mergeCell ref="AW19:BH26"/>
-    <mergeCell ref="AK35:AP36"/>
-    <mergeCell ref="BB10:BC11"/>
-    <mergeCell ref="F30:Q30"/>
-    <mergeCell ref="BD10:BE11"/>
-    <mergeCell ref="F21:Q21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
